--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Contributi allo studio.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Contributi allo studio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="81">
   <si>
     <r>
       <t xml:space="preserve">
@@ -82,7 +82,7 @@
     <t>Domanda di iscrizione al servizio: integrazione documentazione</t>
   </si>
   <si>
-    <t xml:space="preserve">Pubblicazioni graduatorie </t>
+    <t>Pubblicazioni graduatorie</t>
   </si>
   <si>
     <t>Note di compilazione</t>
@@ -146,7 +146,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>Vedi le iniziative</t>
+    <t>Vai alle informazioni</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -530,7 +530,7 @@
     </r>
   </si>
   <si>
-    <t>Inizia</t>
+    <t>-</t>
   </si>
   <si>
     <t>Aggiungi documenti</t>
@@ -556,16 +556,13 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
       <t xml:space="preserve">
 File allegato al messaggio</t>
     </r>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <r>
@@ -1286,46 +1283,46 @@
         <v>72</v>
       </c>
       <c r="B8" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="34" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
+      <c r="B9" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="C9" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="D9" s="34" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="34" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+      <c r="B10" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="C10" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="D10" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="34" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>53</v>
